--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -64186,21 +64174,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Russia WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Coverage: 2016-01-04 to 2026-03-22 | Publication days: 168</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -64208,22 +64196,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3732"/>
+  <dimension ref="A1:E3733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -64150,6 +64150,23 @@
         <v>-2</v>
       </c>
       <c r="E3732" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3733">
+      <c r="A3733" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B3733" t="inlineStr"/>
+      <c r="C3733" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D3733" t="n">
+        <v>-2.033333333333333</v>
+      </c>
+      <c r="E3733" t="b">
         <v>0</v>
       </c>
     </row>
@@ -64183,7 +64200,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2016-01-04 to 2026-03-22 | Publication days: 168</t>
+          <t>Coverage: 2016-01-04 to 2026-03-23 | Publication days: 168</t>
         </is>
       </c>
     </row>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3733"/>
+  <dimension ref="A1:E3734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -64167,6 +64167,23 @@
         <v>-2.033333333333333</v>
       </c>
       <c r="E3733" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3734">
+      <c r="A3734" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B3734" t="inlineStr"/>
+      <c r="C3734" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D3734" t="n">
+        <v>-2.133333333333333</v>
+      </c>
+      <c r="E3734" t="b">
         <v>0</v>
       </c>
     </row>
@@ -64200,7 +64217,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2016-01-04 to 2026-03-23 | Publication days: 168</t>
+          <t>Coverage: 2016-01-04 to 2026-03-24 | Publication days: 168</t>
         </is>
       </c>
     </row>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3734"/>
+  <dimension ref="A1:E3735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -64184,6 +64184,23 @@
         <v>-2.133333333333333</v>
       </c>
       <c r="E3734" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3735">
+      <c r="A3735" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B3735" t="inlineStr"/>
+      <c r="C3735" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D3735" t="n">
+        <v>-2.233333333333333</v>
+      </c>
+      <c r="E3735" t="b">
         <v>0</v>
       </c>
     </row>
@@ -64217,7 +64234,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2016-01-04 to 2026-03-24 | Publication days: 168</t>
+          <t>Coverage: 2016-01-04 to 2026-03-25 | Publication days: 168</t>
         </is>
       </c>
     </row>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -64159,7 +64159,9 @@
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="B3733" t="inlineStr"/>
+      <c r="B3733" t="n">
+        <v>-3</v>
+      </c>
       <c r="C3733" t="n">
         <v>-3</v>
       </c>
@@ -64167,7 +64169,7 @@
         <v>-2.033333333333333</v>
       </c>
       <c r="E3733" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3734">
@@ -64176,7 +64178,9 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="B3734" t="inlineStr"/>
+      <c r="B3734" t="n">
+        <v>-3</v>
+      </c>
       <c r="C3734" t="n">
         <v>-3</v>
       </c>
@@ -64184,7 +64188,7 @@
         <v>-2.133333333333333</v>
       </c>
       <c r="E3734" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3735">
@@ -64234,7 +64238,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2016-01-04 to 2026-03-25 | Publication days: 168</t>
+          <t>Coverage: 2016-01-04 to 2026-03-25 | Publication days: 170</t>
         </is>
       </c>
     </row>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -64229,21 +64241,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Russia WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2016-01-04 to 2026-03-25 | Publication days: 170</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -64251,22 +64263,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3735"/>
+  <dimension ref="A1:E3736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -64209,7 +64197,9 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="B3735" t="inlineStr"/>
+      <c r="B3735" t="n">
+        <v>-3</v>
+      </c>
       <c r="C3735" t="n">
         <v>-3</v>
       </c>
@@ -64217,6 +64207,23 @@
         <v>-2.233333333333333</v>
       </c>
       <c r="E3735" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3736">
+      <c r="A3736" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B3736" t="inlineStr"/>
+      <c r="C3736" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D3736" t="n">
+        <v>-2.233333333333333</v>
+      </c>
+      <c r="E3736" t="b">
         <v>0</v>
       </c>
     </row>
@@ -64241,21 +64248,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Russia WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2016-01-04 to 2026-03-25 | Publication days: 170</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2016-01-04 to 2026-03-26 | Publication days: 171</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -64263,22 +64270,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -64248,21 +64260,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Russia WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2016-01-04 to 2026-03-26 | Publication days: 171</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -64270,22 +64282,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -64260,21 +64248,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Russia WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Coverage: 2016-01-04 to 2026-03-26 | Publication days: 171</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -64282,22 +64270,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3736"/>
+  <dimension ref="A1:E3737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -64228,7 +64216,9 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="B3736" t="inlineStr"/>
+      <c r="B3736" t="n">
+        <v>-3</v>
+      </c>
       <c r="C3736" t="n">
         <v>-3</v>
       </c>
@@ -64236,6 +64226,23 @@
         <v>-2.233333333333333</v>
       </c>
       <c r="E3736" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3737">
+      <c r="A3737" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B3737" t="inlineStr"/>
+      <c r="C3737" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D3737" t="n">
+        <v>-2.233333333333333</v>
+      </c>
+      <c r="E3737" t="b">
         <v>0</v>
       </c>
     </row>
@@ -64260,21 +64267,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Russia WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2016-01-04 to 2026-03-26 | Publication days: 171</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2016-01-04 to 2026-03-27 | Publication days: 172</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -64282,22 +64289,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -64235,15 +64235,17 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="B3737" t="inlineStr"/>
+      <c r="B3737" t="n">
+        <v>2</v>
+      </c>
       <c r="C3737" t="n">
-        <v>-3</v>
+        <v>-2.285714285714286</v>
       </c>
       <c r="D3737" t="n">
-        <v>-2.233333333333333</v>
+        <v>-2.066666666666667</v>
       </c>
       <c r="E3737" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -64276,7 +64278,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2016-01-04 to 2026-03-27 | Publication days: 172</t>
+          <t>Coverage: 2016-01-04 to 2026-03-27 | Publication days: 173</t>
         </is>
       </c>
     </row>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3737"/>
+  <dimension ref="A1:E3738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -64236,15 +64236,34 @@
         </is>
       </c>
       <c r="B3737" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="C3737" t="n">
-        <v>-2.285714285714286</v>
+        <v>-2.857142857142857</v>
       </c>
       <c r="D3737" t="n">
-        <v>-2.066666666666667</v>
+        <v>-2.2</v>
       </c>
       <c r="E3737" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3738">
+      <c r="A3738" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B3738" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C3738" t="n">
+        <v>-2.857142857142857</v>
+      </c>
+      <c r="D3738" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="E3738" t="b">
         <v>1</v>
       </c>
     </row>
@@ -64278,7 +64297,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2016-01-04 to 2026-03-27 | Publication days: 173</t>
+          <t>Coverage: 2016-01-04 to 2026-03-28 | Publication days: 174</t>
         </is>
       </c>
     </row>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3738"/>
+  <dimension ref="A1:E3739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -64265,6 +64265,23 @@
       </c>
       <c r="E3738" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3739">
+      <c r="A3739" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B3739" t="inlineStr"/>
+      <c r="C3739" t="n">
+        <v>-2.857142857142857</v>
+      </c>
+      <c r="D3739" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="E3739" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -64297,7 +64314,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2016-01-04 to 2026-03-28 | Publication days: 174</t>
+          <t>Coverage: 2016-01-04 to 2026-03-29 | Publication days: 174</t>
         </is>
       </c>
     </row>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3739"/>
+  <dimension ref="A1:E3740"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -64273,15 +64273,36 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="B3739" t="inlineStr"/>
+      <c r="B3739" t="n">
+        <v>0</v>
+      </c>
       <c r="C3739" t="n">
-        <v>-2.857142857142857</v>
+        <v>-2.428571428571428</v>
       </c>
       <c r="D3739" t="n">
-        <v>-2.2</v>
+        <v>-2.1</v>
       </c>
       <c r="E3739" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3740">
+      <c r="A3740" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B3740" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C3740" t="n">
+        <v>-2.428571428571428</v>
+      </c>
+      <c r="D3740" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="E3740" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -64314,7 +64335,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2016-01-04 to 2026-03-29 | Publication days: 174</t>
+          <t>Coverage: 2016-01-04 to 2026-03-30 | Publication days: 176</t>
         </is>
       </c>
     </row>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3740"/>
+  <dimension ref="A1:E3741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -64302,6 +64302,25 @@
         <v>-2.1</v>
       </c>
       <c r="E3740" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3741">
+      <c r="A3741" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B3741" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3741" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D3741" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E3741" t="b">
         <v>1</v>
       </c>
     </row>
@@ -64335,7 +64354,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2016-01-04 to 2026-03-30 | Publication days: 176</t>
+          <t>Coverage: 2016-01-04 to 2026-03-31 | Publication days: 177</t>
         </is>
       </c>
     </row>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3741"/>
+  <dimension ref="A1:E3742"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -64322,6 +64322,23 @@
       </c>
       <c r="E3741" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3742">
+      <c r="A3742" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B3742" t="inlineStr"/>
+      <c r="C3742" t="n">
+        <v>-1.571428571428571</v>
+      </c>
+      <c r="D3742" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="E3742" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -64354,7 +64371,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2016-01-04 to 2026-03-31 | Publication days: 177</t>
+          <t>Coverage: 2016-01-04 to 2026-04-01 | Publication days: 177</t>
         </is>
       </c>
     </row>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3742"/>
+  <dimension ref="A1:E3743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -64330,7 +64330,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="B3742" t="inlineStr"/>
+      <c r="B3742" t="n">
+        <v>0</v>
+      </c>
       <c r="C3742" t="n">
         <v>-1.571428571428571</v>
       </c>
@@ -64338,6 +64340,23 @@
         <v>-1.9</v>
       </c>
       <c r="E3742" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3743">
+      <c r="A3743" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B3743" t="inlineStr"/>
+      <c r="C3743" t="n">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="D3743" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="E3743" t="b">
         <v>0</v>
       </c>
     </row>
@@ -64371,7 +64390,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2016-01-04 to 2026-04-01 | Publication days: 177</t>
+          <t>Coverage: 2016-01-04 to 2026-04-02 | Publication days: 178</t>
         </is>
       </c>
     </row>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3743"/>
+  <dimension ref="A1:E3744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -64357,6 +64357,23 @@
         <v>-1.9</v>
       </c>
       <c r="E3743" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3744">
+      <c r="A3744" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B3744" t="inlineStr"/>
+      <c r="C3744" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D3744" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="E3744" t="b">
         <v>0</v>
       </c>
     </row>
@@ -64390,7 +64407,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2016-01-04 to 2026-04-02 | Publication days: 178</t>
+          <t>Coverage: 2016-01-04 to 2026-04-03 | Publication days: 178</t>
         </is>
       </c>
     </row>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3744"/>
+  <dimension ref="A1:E3745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -64349,15 +64349,17 @@
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="B3743" t="inlineStr"/>
+      <c r="B3743" t="n">
+        <v>-2</v>
+      </c>
       <c r="C3743" t="n">
-        <v>-1.142857142857143</v>
+        <v>-1.428571428571429</v>
       </c>
       <c r="D3743" t="n">
-        <v>-1.9</v>
+        <v>-1.966666666666667</v>
       </c>
       <c r="E3743" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3744">
@@ -64366,14 +64368,33 @@
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="B3744" t="inlineStr"/>
+      <c r="B3744" t="n">
+        <v>-3</v>
+      </c>
       <c r="C3744" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D3744" t="n">
-        <v>-1.8</v>
+        <v>-1.966666666666667</v>
       </c>
       <c r="E3744" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3745">
+      <c r="A3745" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B3745" t="inlineStr"/>
+      <c r="C3745" t="n">
+        <v>-1.571428571428571</v>
+      </c>
+      <c r="D3745" t="n">
+        <v>-1.966666666666667</v>
+      </c>
+      <c r="E3745" t="b">
         <v>0</v>
       </c>
     </row>
@@ -64407,7 +64428,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2016-01-04 to 2026-04-03 | Publication days: 178</t>
+          <t>Coverage: 2016-01-04 to 2026-04-04 | Publication days: 180</t>
         </is>
       </c>
     </row>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3745"/>
+  <dimension ref="A1:E3746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -64387,7 +64387,9 @@
           <t>2026-04-04</t>
         </is>
       </c>
-      <c r="B3745" t="inlineStr"/>
+      <c r="B3745" t="n">
+        <v>-3</v>
+      </c>
       <c r="C3745" t="n">
         <v>-1.571428571428571</v>
       </c>
@@ -64395,6 +64397,23 @@
         <v>-1.966666666666667</v>
       </c>
       <c r="E3745" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3746">
+      <c r="A3746" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B3746" t="inlineStr"/>
+      <c r="C3746" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D3746" t="n">
+        <v>-1.966666666666667</v>
+      </c>
+      <c r="E3746" t="b">
         <v>0</v>
       </c>
     </row>
@@ -64428,7 +64447,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2016-01-04 to 2026-04-04 | Publication days: 180</t>
+          <t>Coverage: 2016-01-04 to 2026-04-05 | Publication days: 181</t>
         </is>
       </c>
     </row>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3746"/>
+  <dimension ref="A1:E3747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -64414,6 +64414,23 @@
         <v>-1.966666666666667</v>
       </c>
       <c r="E3746" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3747">
+      <c r="A3747" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B3747" t="inlineStr"/>
+      <c r="C3747" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D3747" t="n">
+        <v>-2.133333333333333</v>
+      </c>
+      <c r="E3747" t="b">
         <v>0</v>
       </c>
     </row>
@@ -64447,7 +64464,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2016-01-04 to 2026-04-05 | Publication days: 181</t>
+          <t>Coverage: 2016-01-04 to 2026-04-06 | Publication days: 181</t>
         </is>
       </c>
     </row>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3747"/>
+  <dimension ref="A1:E3748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -64406,15 +64406,17 @@
           <t>2026-04-05</t>
         </is>
       </c>
-      <c r="B3746" t="inlineStr"/>
+      <c r="B3746" t="n">
+        <v>0</v>
+      </c>
       <c r="C3746" t="n">
-        <v>-2</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D3746" t="n">
-        <v>-1.966666666666667</v>
+        <v>-1.866666666666667</v>
       </c>
       <c r="E3746" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3747">
@@ -64423,15 +64425,36 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="B3747" t="inlineStr"/>
+      <c r="B3747" t="n">
+        <v>-3</v>
+      </c>
       <c r="C3747" t="n">
+        <v>-1.571428571428571</v>
+      </c>
+      <c r="D3747" t="n">
+        <v>-2.033333333333333</v>
+      </c>
+      <c r="E3747" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3748">
+      <c r="A3748" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B3748" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C3748" t="n">
         <v>-2</v>
       </c>
-      <c r="D3747" t="n">
+      <c r="D3748" t="n">
         <v>-2.133333333333333</v>
       </c>
-      <c r="E3747" t="b">
-        <v>0</v>
+      <c r="E3748" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -64464,7 +64487,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2016-01-04 to 2026-04-06 | Publication days: 181</t>
+          <t>Coverage: 2016-01-04 to 2026-04-07 | Publication days: 184</t>
         </is>
       </c>
     </row>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3748"/>
+  <dimension ref="A1:E3749"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -64454,6 +64454,25 @@
         <v>-2.133333333333333</v>
       </c>
       <c r="E3748" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3749">
+      <c r="A3749" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B3749" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C3749" t="n">
+        <v>-2.428571428571428</v>
+      </c>
+      <c r="D3749" t="n">
+        <v>-2.233333333333333</v>
+      </c>
+      <c r="E3749" t="b">
         <v>1</v>
       </c>
     </row>
@@ -64487,7 +64506,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2016-01-04 to 2026-04-07 | Publication days: 184</t>
+          <t>Coverage: 2016-01-04 to 2026-04-08 | Publication days: 185</t>
         </is>
       </c>
     </row>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3749"/>
+  <dimension ref="A1:E3750"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -64473,6 +64473,25 @@
         <v>-2.233333333333333</v>
       </c>
       <c r="E3749" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3750">
+      <c r="A3750" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B3750" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C3750" t="n">
+        <v>-2.428571428571428</v>
+      </c>
+      <c r="D3750" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="E3750" t="b">
         <v>1</v>
       </c>
     </row>
@@ -64506,7 +64525,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2016-01-04 to 2026-04-08 | Publication days: 185</t>
+          <t>Coverage: 2016-01-04 to 2026-04-09 | Publication days: 186</t>
         </is>
       </c>
     </row>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3750"/>
+  <dimension ref="A1:E3751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -64492,6 +64492,25 @@
         <v>-2.3</v>
       </c>
       <c r="E3750" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3751">
+      <c r="A3751" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B3751" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C3751" t="n">
+        <v>-2.428571428571428</v>
+      </c>
+      <c r="D3751" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="E3751" t="b">
         <v>1</v>
       </c>
     </row>
@@ -64525,7 +64544,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2016-01-04 to 2026-04-09 | Publication days: 186</t>
+          <t>Coverage: 2016-01-04 to 2026-04-10 | Publication days: 187</t>
         </is>
       </c>
     </row>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3751"/>
+  <dimension ref="A1:E3752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -64512,6 +64512,23 @@
       </c>
       <c r="E3751" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3752">
+      <c r="A3752" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B3752" t="inlineStr"/>
+      <c r="C3752" t="n">
+        <v>-2.428571428571428</v>
+      </c>
+      <c r="D3752" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="E3752" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -64544,7 +64561,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2016-01-04 to 2026-04-10 | Publication days: 187</t>
+          <t>Coverage: 2016-01-04 to 2026-04-11 | Publication days: 187</t>
         </is>
       </c>
     </row>

--- a/data/RU.xlsx
+++ b/data/RU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3752"/>
+  <dimension ref="A1:E3753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -64520,14 +64520,33 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="B3752" t="inlineStr"/>
+      <c r="B3752" t="n">
+        <v>0</v>
+      </c>
       <c r="C3752" t="n">
-        <v>-2.428571428571428</v>
+        <v>-2</v>
       </c>
       <c r="D3752" t="n">
-        <v>-2.3</v>
+        <v>-2.2</v>
       </c>
       <c r="E3752" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3753">
+      <c r="A3753" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B3753" t="inlineStr"/>
+      <c r="C3753" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D3753" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="E3753" t="b">
         <v>0</v>
       </c>
     </row>
@@ -64561,7 +64580,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2016-01-04 to 2026-04-11 | Publication days: 187</t>
+          <t>Coverage: 2016-01-04 to 2026-04-12 | Publication days: 188</t>
         </is>
       </c>
     </row>
